--- a/locomo_experiment/experiment_results.xlsx
+++ b/locomo_experiment/experiment_results.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2007,6 +2007,936 @@
         <v>4098855</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e0_baseline</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.6432160804020101</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0.2004610529283482</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>0.9619565217391305</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>0.8185328185328186</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>0.8844680675537119</v>
+      </c>
+      <c r="T16" s="7" t="n">
+        <v>0.005434782608695652</v>
+      </c>
+      <c r="U16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W16" s="6" t="n"/>
+      <c r="X16" s="6" t="n"/>
+      <c r="Y16" s="6" t="n"/>
+      <c r="Z16" s="6" t="n"/>
+      <c r="AA16" s="6" t="n"/>
+      <c r="AB16" s="6" t="n"/>
+      <c r="AC16" s="6" t="n">
+        <v>933082</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e0_nosum</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0.6582914572864321</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>0.1794610582114781</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="O17" s="7" t="n">
+        <v>0.7571428571428571</v>
+      </c>
+      <c r="P17" s="7" t="n">
+        <v>0.9148936170212766</v>
+      </c>
+      <c r="Q17" s="7" t="n">
+        <v>0.9673913043478261</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v>0.81875</v>
+      </c>
+      <c r="S17" s="7" t="n">
+        <v>0.8868857447132207</v>
+      </c>
+      <c r="T17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W17" s="6" t="n"/>
+      <c r="X17" s="6" t="n"/>
+      <c r="Y17" s="6" t="n"/>
+      <c r="Z17" s="6" t="n"/>
+      <c r="AA17" s="6" t="n"/>
+      <c r="AB17" s="6" t="n"/>
+      <c r="AC17" s="6" t="n">
+        <v>580666</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e1_m1</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0.6733668341708543</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>0.2078083524215598</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>0.9673913043478261</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v>0.8300653594771242</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <v>0.8934824710485751</v>
+      </c>
+      <c r="T18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W18" s="6" t="n"/>
+      <c r="X18" s="6" t="n"/>
+      <c r="Y18" s="6" t="n"/>
+      <c r="Z18" s="6" t="n"/>
+      <c r="AA18" s="6" t="n"/>
+      <c r="AB18" s="6" t="n"/>
+      <c r="AC18" s="6" t="n">
+        <v>940139</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e1_nosum</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0.6582914572864321</v>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>0.1849192954800603</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0.4054054054054054</v>
+      </c>
+      <c r="N19" s="7" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="O19" s="7" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="P19" s="7" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="R19" s="7" t="n">
+        <v>0.8239895697522817</v>
+      </c>
+      <c r="S19" s="7" t="n">
+        <v>0.8853231454950653</v>
+      </c>
+      <c r="T19" s="7" t="n">
+        <v>0.005434782608695652</v>
+      </c>
+      <c r="U19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W19" s="6" t="n"/>
+      <c r="X19" s="6" t="n"/>
+      <c r="Y19" s="6" t="n"/>
+      <c r="Z19" s="6" t="n"/>
+      <c r="AA19" s="6" t="n"/>
+      <c r="AB19" s="6" t="n"/>
+      <c r="AC19" s="6" t="n">
+        <v>589272</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e2_m1_m3</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0.6683417085427136</v>
+      </c>
+      <c r="K20" s="7" t="n">
+        <v>0.2104976301358845</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="N20" s="7" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="O20" s="7" t="n">
+        <v>0.8142857142857143</v>
+      </c>
+      <c r="P20" s="7" t="n">
+        <v>0.851063829787234</v>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>0.9619565217391305</v>
+      </c>
+      <c r="R20" s="7" t="n">
+        <v>0.822477650063857</v>
+      </c>
+      <c r="S20" s="7" t="n">
+        <v>0.8867659586054526</v>
+      </c>
+      <c r="T20" s="7" t="n">
+        <v>0.005434782608695652</v>
+      </c>
+      <c r="U20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W20" s="6" t="n"/>
+      <c r="X20" s="6" t="n"/>
+      <c r="Y20" s="6" t="n"/>
+      <c r="Z20" s="6" t="n"/>
+      <c r="AA20" s="6" t="n"/>
+      <c r="AB20" s="6" t="n"/>
+      <c r="AC20" s="6" t="n">
+        <v>979815</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e3_m1_m4</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0.6834170854271356</v>
+      </c>
+      <c r="K21" s="7" t="n">
+        <v>0.1988597346110624</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.2972972972972973</v>
+      </c>
+      <c r="N21" s="7" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="O21" s="7" t="n">
+        <v>0.8285714285714286</v>
+      </c>
+      <c r="P21" s="7" t="n">
+        <v>0.8723404255319149</v>
+      </c>
+      <c r="Q21" s="7" t="n">
+        <v>0.9728260869565217</v>
+      </c>
+      <c r="R21" s="7" t="n">
+        <v>0.8268229166666666</v>
+      </c>
+      <c r="S21" s="7" t="n">
+        <v>0.8939019786718675</v>
+      </c>
+      <c r="T21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W21" s="6" t="n"/>
+      <c r="X21" s="6" t="n"/>
+      <c r="Y21" s="6" t="n"/>
+      <c r="Z21" s="6" t="n"/>
+      <c r="AA21" s="6" t="n"/>
+      <c r="AB21" s="6" t="n"/>
+      <c r="AC21" s="6" t="n">
+        <v>951391</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>structmem-ablate_e4_full</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0.678391959798995</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>0.1945078861070313</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0.3243243243243243</v>
+      </c>
+      <c r="N22" s="7" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="O22" s="7" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="P22" s="7" t="n">
+        <v>0.9361702127659575</v>
+      </c>
+      <c r="Q22" s="7" t="n">
+        <v>0.9619565217391305</v>
+      </c>
+      <c r="R22" s="7" t="n">
+        <v>0.8272727272727273</v>
+      </c>
+      <c r="S22" s="7" t="n">
+        <v>0.8895454796487546</v>
+      </c>
+      <c r="T22" s="7" t="n">
+        <v>0.005434782608695652</v>
+      </c>
+      <c r="U22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W22" s="6" t="n"/>
+      <c r="X22" s="6" t="n"/>
+      <c r="Y22" s="6" t="n"/>
+      <c r="Z22" s="6" t="n"/>
+      <c r="AA22" s="6" t="n"/>
+      <c r="AB22" s="6" t="n"/>
+      <c r="AC22" s="6" t="n">
+        <v>994644</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>structmem-sm_31b</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>0.6733668341708543</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>0.1912391163211874</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.7027027027027027</v>
+      </c>
+      <c r="N23" s="7" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="O23" s="7" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="P23" s="7" t="n">
+        <v>0.9787234042553191</v>
+      </c>
+      <c r="Q23" s="7" t="n">
+        <v>0.7989130434782609</v>
+      </c>
+      <c r="R23" s="7" t="n">
+        <v>0.833916083916084</v>
+      </c>
+      <c r="S23" s="7" t="n">
+        <v>0.81603938272467</v>
+      </c>
+      <c r="T23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W23" s="6" t="n"/>
+      <c r="X23" s="6" t="n"/>
+      <c r="Y23" s="6" t="n"/>
+      <c r="Z23" s="6" t="n"/>
+      <c r="AA23" s="6" t="n"/>
+      <c r="AB23" s="6" t="n"/>
+      <c r="AC23" s="6" t="n">
+        <v>369110</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>structmem-sm_cost</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.6834170854271356</v>
+      </c>
+      <c r="K24" s="7" t="n">
+        <v>0.1962273845103919</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0.7027027027027027</v>
+      </c>
+      <c r="N24" s="7" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="O24" s="7" t="n">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="P24" s="7" t="n">
+        <v>0.9574468085106383</v>
+      </c>
+      <c r="Q24" s="7" t="n">
+        <v>0.7445652173913043</v>
+      </c>
+      <c r="R24" s="7" t="n">
+        <v>0.8193430656934306</v>
+      </c>
+      <c r="S24" s="7" t="n">
+        <v>0.7801664003246835</v>
+      </c>
+      <c r="T24" s="7" t="n">
+        <v>0.005434782608695652</v>
+      </c>
+      <c r="U24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W24" s="6" t="n"/>
+      <c r="X24" s="6" t="n"/>
+      <c r="Y24" s="6" t="n"/>
+      <c r="Z24" s="6" t="n"/>
+      <c r="AA24" s="6" t="n"/>
+      <c r="AB24" s="6" t="n"/>
+      <c r="AC24" s="6" t="n">
+        <v>377631</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>structmem-upd_31b</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>StructMem</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>all-MiniLM-L6-v2</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.678391959798995</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>0.1987125744317359</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0.7027027027027027</v>
+      </c>
+      <c r="N25" s="7" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="O25" s="7" t="n">
+        <v>0.5857142857142857</v>
+      </c>
+      <c r="P25" s="7" t="n">
+        <v>0.9787234042553191</v>
+      </c>
+      <c r="Q25" s="7" t="n">
+        <v>0.7934782608695652</v>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>0.8210526315789474</v>
+      </c>
+      <c r="S25" s="7" t="n">
+        <v>0.807029976613989</v>
+      </c>
+      <c r="T25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>session</t>
+        </is>
+      </c>
+      <c r="W25" s="6" t="n"/>
+      <c r="X25" s="6" t="n"/>
+      <c r="Y25" s="6" t="n"/>
+      <c r="Z25" s="6" t="n"/>
+      <c r="AA25" s="6" t="n"/>
+      <c r="AB25" s="6" t="n"/>
+      <c r="AC25" s="6" t="n">
+        <v>396763</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
